--- a/backtest_runs/20260410_193731/by_symbol/CLVL/CLVL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/CLVL/CLVL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>108411.04</v>
@@ -771,7 +771,7 @@
         <v>-5841</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>102570.04</v>
@@ -817,7 +817,7 @@
         <v>-6541.919999999999</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>96028.12</v>
@@ -909,7 +909,7 @@
         <v>-545.1600000000022</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>101791.24</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>104127.64</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>104127.64</v>
@@ -1093,7 +1093,7 @@
         <v>-155.7599999999967</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>103971.88</v>
@@ -1185,7 +1185,7 @@
         <v>-4127.640000000009</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>102959.44</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>102959.44</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>102959.44</v>
@@ -1415,7 +1415,7 @@
         <v>-3894</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>111682</v>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>112071.4</v>
@@ -1645,7 +1645,7 @@
         <v>-9890.759999999997</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>102180.64</v>
